--- a/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ETH_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6907A41-6D53-4007-BB8F-8A12F3884D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20F2E839-8969-41D6-87F0-D639F5EBD159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -804,13 +804,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S01aH05,S01aH03,S02aH04,S02aH05,S03aH02,S03aH04,S03aH03,S01aH02,S04aH04,S04aH05,S01aH04,S04aH02,S03aH05,S04aH03,S02aH03</t>
+    <t>S01aH04,S04aH03,S03aH03,S04aH02,S01aH05,S04aH05,S03aH04,S02aH02,S02aH03,S03aH05,S02aH04,S02aH05,S01aH03,S03aH02,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S02aH06,S03aH06,S01aH06,S02aH01,S01aH01,S04aH01,S04aH06</t>
+    <t>S02aH01,S01aH06,S03aH01,S01aH01,S04aH01,S04aH06,S02aH06,S03aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S02aH06,S03aH06,S01aH06,S02aH01,S01aH01,S04aH01,S04aH06</v>
+        <v>S02aH01,S01aH06,S03aH01,S01aH01,S04aH01,S04aH06,S02aH06,S03aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH02,S01aH05,S01aH03,S02aH04,S02aH05,S03aH02,S03aH04,S03aH03,S01aH02,S04aH04,S04aH05,S01aH04,S04aH02,S03aH05,S04aH03,S02aH03</v>
+        <v>S01aH04,S04aH03,S03aH03,S04aH02,S01aH05,S04aH05,S03aH04,S02aH02,S02aH03,S03aH05,S02aH04,S02aH05,S01aH03,S03aH02,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1533,7 +1533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4A8A96-3C5C-462D-B3E3-8CB14A08CCAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD44B1D-5E8D-4A85-8378-8B426C11BB1E}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1639,7 +1639,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB80609-4800-41F1-A529-1161DBDD8C94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4BD58F-F071-4613-BBAC-5270C5809537}">
   <dimension ref="B9:O1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30789,7 +30789,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07D7E68-7ED7-4294-8040-40B3C961A2B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2C8094-888C-4051-AD3F-5BF647595F0D}">
   <dimension ref="B9:DH78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42812,7 +42812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4E9687-B8B8-4436-9EEB-80BD23C35374}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7705AD63-D96B-4754-AAEE-4B74D6754B16}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43178,7 +43178,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8722966B-865F-4D79-B10F-E80281BF91F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A62C1F0-BA9F-41EF-AD9B-A89E2A91FC0D}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43733,7 +43733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD79EC9-CCDD-43EF-936F-B2E5430C5BCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC8EBF58-9BED-4318-9C6E-8072F50AB637}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44024,7 +44024,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB537D4-4055-463B-9E55-DBD270FA2F7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4D2305-04E6-4947-A182-5A836669FDD1}">
   <dimension ref="B9:E114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44056,7 +44056,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.39223333333333327</v>
+        <v>0.39223333333333338</v>
       </c>
       <c r="E11" t="s">
         <v>262</v>
@@ -44098,7 +44098,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.4888333333333334</v>
+        <v>0.48883333333333329</v>
       </c>
       <c r="E14" t="s">
         <v>262</v>
@@ -44140,7 +44140,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.53706666666666669</v>
+        <v>0.53706666666666658</v>
       </c>
       <c r="E17" t="s">
         <v>262</v>
@@ -44196,7 +44196,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.53259999999999996</v>
+        <v>0.53260000000000007</v>
       </c>
       <c r="E21" t="s">
         <v>262</v>
@@ -44238,7 +44238,7 @@
         <v>41</v>
       </c>
       <c r="D24">
-        <v>0.40090000000000003</v>
+        <v>0.40089999999999998</v>
       </c>
       <c r="E24" t="s">
         <v>262</v>
@@ -44322,7 +44322,7 @@
         <v>45</v>
       </c>
       <c r="D30">
-        <v>0.39490000000000003</v>
+        <v>0.39489999999999997</v>
       </c>
       <c r="E30" t="s">
         <v>262</v>
@@ -44378,7 +44378,7 @@
         <v>45</v>
       </c>
       <c r="D34">
-        <v>0.4196333333333333</v>
+        <v>0.41963333333333336</v>
       </c>
       <c r="E34" t="s">
         <v>262</v>
@@ -44406,7 +44406,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.37916666666666671</v>
+        <v>0.37916666666666665</v>
       </c>
       <c r="E36" t="s">
         <v>262</v>
@@ -44532,7 +44532,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.34200000000000003</v>
+        <v>0.34199999999999992</v>
       </c>
       <c r="E45" t="s">
         <v>262</v>
@@ -44616,7 +44616,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.46533333333333332</v>
+        <v>0.46533333333333338</v>
       </c>
       <c r="E51" t="s">
         <v>262</v>
@@ -44700,7 +44700,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.54570000000000007</v>
+        <v>0.54569999999999996</v>
       </c>
       <c r="E57" t="s">
         <v>262</v>
@@ -44756,7 +44756,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.43393333333333334</v>
+        <v>0.43393333333333328</v>
       </c>
       <c r="E61" t="s">
         <v>262</v>
@@ -44826,7 +44826,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.37793333333333329</v>
+        <v>0.3779333333333334</v>
       </c>
       <c r="E66" t="s">
         <v>262</v>
@@ -44854,7 +44854,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.4336666666666667</v>
+        <v>0.43366666666666664</v>
       </c>
       <c r="E68" t="s">
         <v>262</v>
@@ -44882,7 +44882,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.49970000000000003</v>
+        <v>0.49969999999999998</v>
       </c>
       <c r="E70" t="s">
         <v>262</v>
@@ -44896,7 +44896,7 @@
         <v>37</v>
       </c>
       <c r="D71">
-        <v>0.43906666666666666</v>
+        <v>0.43906666666666672</v>
       </c>
       <c r="E71" t="s">
         <v>262</v>
@@ -44938,7 +44938,7 @@
         <v>45</v>
       </c>
       <c r="D74">
-        <v>0.46956666666666669</v>
+        <v>0.46956666666666663</v>
       </c>
       <c r="E74" t="s">
         <v>262</v>
@@ -44952,7 +44952,7 @@
         <v>37</v>
       </c>
       <c r="D75">
-        <v>0.48066666666666663</v>
+        <v>0.48066666666666674</v>
       </c>
       <c r="E75" t="s">
         <v>262</v>
@@ -45064,7 +45064,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.40100000000000002</v>
+        <v>0.40099999999999997</v>
       </c>
       <c r="E83" t="s">
         <v>262</v>
@@ -45092,7 +45092,7 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>0.41593333333333332</v>
+        <v>0.41593333333333327</v>
       </c>
       <c r="E85" t="s">
         <v>262</v>
@@ -45148,7 +45148,7 @@
         <v>43</v>
       </c>
       <c r="D89">
-        <v>0.43319999999999997</v>
+        <v>0.43320000000000003</v>
       </c>
       <c r="E89" t="s">
         <v>262</v>
@@ -45162,7 +45162,7 @@
         <v>45</v>
       </c>
       <c r="D90">
-        <v>0.42829999999999996</v>
+        <v>0.42830000000000007</v>
       </c>
       <c r="E90" t="s">
         <v>262</v>
@@ -45232,7 +45232,7 @@
         <v>37</v>
       </c>
       <c r="D95">
-        <v>0.34030000000000005</v>
+        <v>0.34029999999999999</v>
       </c>
       <c r="E95" t="s">
         <v>262</v>
@@ -45260,7 +45260,7 @@
         <v>43</v>
       </c>
       <c r="D97">
-        <v>0.51816666666666678</v>
+        <v>0.51816666666666666</v>
       </c>
       <c r="E97" t="s">
         <v>262</v>
@@ -45274,7 +45274,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.41993333333333327</v>
+        <v>0.41993333333333333</v>
       </c>
       <c r="E98" t="s">
         <v>262</v>
@@ -45302,7 +45302,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.5396333333333333</v>
+        <v>0.53963333333333341</v>
       </c>
       <c r="E100" t="s">
         <v>262</v>
@@ -45358,7 +45358,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.50583333333333336</v>
+        <v>0.50583333333333325</v>
       </c>
       <c r="E104" t="s">
         <v>262</v>
@@ -45484,7 +45484,7 @@
         <v>43</v>
       </c>
       <c r="D113">
-        <v>0.52856666666666663</v>
+        <v>0.52856666666666674</v>
       </c>
       <c r="E113" t="s">
         <v>262</v>
